--- a/e2e/expectedData/sub_Master_Benefit_Pulsa.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_Pulsa.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>DAFTAR PEMBAYARAN PULSA KARYAWAN</t>
   </si>
@@ -59,24 +59,27 @@
     <t>IV</t>
   </si>
   <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Phone Credit</t>
+  </si>
+  <si>
+    <t>$ 60.00</t>
+  </si>
+  <si>
+    <t>Jan-26</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>Phone Credit</t>
-  </si>
-  <si>
-    <t>$ 60.00</t>
-  </si>
-  <si>
-    <t>Jan-26</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
     <t>$ 10.00</t>
   </si>
   <si>
@@ -95,7 +98,7 @@
     <t>$ 80.00</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -629,19 +632,19 @@
         <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -652,30 +655,30 @@
         <v>91015</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -685,7 +688,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -693,18 +696,18 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11"/>
       <c r="G11"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12"/>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:9" customHeight="1" ht="37.5">
@@ -714,20 +717,20 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15"/>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/sub_Master_Benefit_Pulsa.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_Pulsa.xlsx
@@ -77,7 +77,7 @@
     <t>VI</t>
   </si>
   <si>
-    <t>Expat</t>
+    <t>Outsource</t>
   </si>
   <si>
     <t>$ 10.00</t>
@@ -98,7 +98,7 @@
     <t>$ 80.00</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
